--- a/deliverables/exports/track-b/05-buying-committee.xlsx
+++ b/deliverables/exports/track-b/05-buying-committee.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -606,26 +606,40 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>**What to offer them.** Access at a price that is honest about what does not exist yet, and permanent terms as the group that took the risk. Not a discount framed as a favour, an exchange: a lower price and direct founder access, for feedback, for being visible in the room, and for permission to reference their experience later.</t>
+          <t>**What to offer them.** Access at a price that is honest about what does not exist yet, and permanent terms as the group that took the risk. Not a discount framed as a favour, an exchange: a lower price and direct founder access, for feedback, for being visible in the room, and for permission to reference their experience.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>**The founder credential problem is at its sharpest here.** These 8 to 12 people are being asked to commit before there is anything to evaluate. `00-ASSUMPTIONS.md` decision 5 is not an empty field in a template at this point, it is the entire pitch. Until the founder can say what they have actually done, founding cohort outreach is a conversation with no evidence in it.</t>
+          <t>**Permission is agreed at joining, in writing, not requested at the end.** Resolved as conflict 5 in `00-RESOLUTIONS.md`. Asking afterwards produces a polite decline from a member who is otherwise happy, and Phase 6 stays blocked for another six months. The Block 1 research is specific about what a North American buyer counts as proof: named, attributable, with job title, company size and a concrete use case. Generic praise is discounted. So the cohort agreement should name what will be published and in what form, and members should know that before they join rather than be asked to improvise it later.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
+          <t>This makes the founding cohort the business's proof-generation mechanism rather than just its first customers. It is currently the only one available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>**The founder credential problem is at its sharpest here.** These 8 to 12 people are being asked to commit before there is anything to evaluate. `00-ASSUMPTIONS.md` decision 5 is not an empty field in a template at this point, it is the entire pitch. Until the founder can say what they have actually done, founding cohort outreach is a conversation with no evidence in it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Carried forward</t>
         </is>
